--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_11-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_11-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443B1AEE-166E-4C37-BB09-842E31102C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7A9801-AF22-41FE-92E8-C2D3E9CAEC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33945" yWindow="1470" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33690" yWindow="1920" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -640,9 +640,6 @@
     <t>£577.15</t>
   </si>
   <si>
-    <t>£141.19</t>
-  </si>
-  <si>
     <t>£836.5</t>
   </si>
   <si>
@@ -664,9 +661,6 @@
     <t>£654.15</t>
   </si>
   <si>
-    <t>£143.21</t>
-  </si>
-  <si>
     <t>£659.55</t>
   </si>
   <si>
@@ -806,6 +800,12 @@
   </si>
   <si>
     <t>£711.4</t>
+  </si>
+  <si>
+    <t>£705.95</t>
+  </si>
+  <si>
+    <t>£716.05</t>
   </si>
 </sst>
 </file>
@@ -1256,7 +1256,7 @@
         <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K2" t="s">
         <v>24</v>
@@ -1300,7 +1300,7 @@
         <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G3" t="s">
         <v>35</v>
@@ -1324,7 +1324,7 @@
         <v>40</v>
       </c>
       <c r="N3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O3" t="s">
         <v>41</v>
@@ -1356,7 +1356,7 @@
         <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G4" t="s">
         <v>47</v>
@@ -1380,7 +1380,7 @@
         <v>52</v>
       </c>
       <c r="N4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O4" t="s">
         <v>53</v>
@@ -1412,7 +1412,7 @@
         <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G5" t="s">
         <v>58</v>
@@ -1424,7 +1424,7 @@
         <v>60</v>
       </c>
       <c r="J5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K5" t="s">
         <v>61</v>
@@ -1436,7 +1436,7 @@
         <v>62</v>
       </c>
       <c r="N5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="O5" t="s">
         <v>63</v>
@@ -1468,7 +1468,7 @@
         <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G6" t="s">
         <v>69</v>
@@ -1480,7 +1480,7 @@
         <v>71</v>
       </c>
       <c r="J6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K6" t="s">
         <v>72</v>
@@ -1492,7 +1492,7 @@
         <v>73</v>
       </c>
       <c r="N6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O6" t="s">
         <v>74</v>
@@ -1524,7 +1524,7 @@
         <v>78</v>
       </c>
       <c r="F7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G7" t="s">
         <v>79</v>
@@ -1580,7 +1580,7 @@
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G8" t="s">
         <v>89</v>
@@ -1592,7 +1592,7 @@
         <v>90</v>
       </c>
       <c r="J8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K8" t="s">
         <v>91</v>
@@ -1604,7 +1604,7 @@
         <v>92</v>
       </c>
       <c r="N8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O8" t="s">
         <v>93</v>
@@ -1636,7 +1636,7 @@
         <v>97</v>
       </c>
       <c r="F9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G9" t="s">
         <v>98</v>
@@ -1660,7 +1660,7 @@
         <v>103</v>
       </c>
       <c r="N9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="O9" t="s">
         <v>104</v>
@@ -1692,7 +1692,7 @@
         <v>109</v>
       </c>
       <c r="F10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G10" t="s">
         <v>110</v>
@@ -1704,7 +1704,7 @@
         <v>112</v>
       </c>
       <c r="J10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K10" t="s">
         <v>102</v>
@@ -1748,7 +1748,7 @@
         <v>109</v>
       </c>
       <c r="F11" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G11" t="s">
         <v>117</v>
@@ -1760,7 +1760,7 @@
         <v>119</v>
       </c>
       <c r="J11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K11" t="s">
         <v>120</v>
@@ -1772,7 +1772,7 @@
         <v>121</v>
       </c>
       <c r="N11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="O11" t="s">
         <v>122</v>
@@ -1804,7 +1804,7 @@
         <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G12" t="s">
         <v>128</v>
@@ -1816,7 +1816,7 @@
         <v>129</v>
       </c>
       <c r="J12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K12" t="s">
         <v>25</v>
@@ -1860,7 +1860,7 @@
         <v>134</v>
       </c>
       <c r="F13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G13" t="s">
         <v>135</v>
@@ -1884,7 +1884,7 @@
         <v>140</v>
       </c>
       <c r="N13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O13" t="s">
         <v>141</v>
@@ -1916,7 +1916,7 @@
         <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G14" t="s">
         <v>146</v>
@@ -1928,7 +1928,7 @@
         <v>148</v>
       </c>
       <c r="J14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="K14" t="s">
         <v>149</v>
@@ -1940,7 +1940,7 @@
         <v>150</v>
       </c>
       <c r="N14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O14" t="s">
         <v>151</v>
@@ -1972,7 +1972,7 @@
         <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G15" t="s">
         <v>155</v>
@@ -1996,7 +1996,7 @@
         <v>160</v>
       </c>
       <c r="N15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O15" t="s">
         <v>161</v>
@@ -2028,7 +2028,7 @@
         <v>165</v>
       </c>
       <c r="F16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G16" t="s">
         <v>166</v>
@@ -2040,7 +2040,7 @@
         <v>29</v>
       </c>
       <c r="J16" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K16" t="s">
         <v>168</v>
@@ -2052,7 +2052,7 @@
         <v>169</v>
       </c>
       <c r="N16" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="O16" t="s">
         <v>170</v>
@@ -2264,7 +2264,7 @@
         <v>25</v>
       </c>
       <c r="J20" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K20" t="s">
         <v>25</v>
@@ -2320,7 +2320,7 @@
         <v>25</v>
       </c>
       <c r="J21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K21" t="s">
         <v>25</v>
@@ -2435,36 +2435,36 @@
         <v>25</v>
       </c>
       <c r="K23" t="s">
+        <v>260</v>
+      </c>
+      <c r="L23" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" t="s">
         <v>206</v>
       </c>
-      <c r="L23" t="s">
-        <v>25</v>
-      </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
+        <v>258</v>
+      </c>
+      <c r="O23" t="s">
         <v>207</v>
       </c>
-      <c r="N23" t="s">
-        <v>260</v>
-      </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>25</v>
+      </c>
+      <c r="R23" t="s">
         <v>208</v>
-      </c>
-      <c r="P23" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>25</v>
-      </c>
-      <c r="R23" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>209</v>
+      </c>
+      <c r="B24" t="s">
         <v>210</v>
-      </c>
-      <c r="B24" t="s">
-        <v>211</v>
       </c>
       <c r="C24" t="s">
         <v>203</v>
@@ -2479,11 +2479,11 @@
         <v>25</v>
       </c>
       <c r="G24" t="s">
+        <v>211</v>
+      </c>
+      <c r="H24" t="s">
         <v>212</v>
       </c>
-      <c r="H24" t="s">
-        <v>213</v>
-      </c>
       <c r="I24" t="s">
         <v>25</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>25</v>
       </c>
       <c r="K24" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
       <c r="L24" t="s">
         <v>25</v>
@@ -2500,10 +2500,10 @@
         <v>29</v>
       </c>
       <c r="N24" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="O24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="P24" t="s">
         <v>25</v>
@@ -2512,42 +2512,42 @@
         <v>25</v>
       </c>
       <c r="R24" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>215</v>
+      </c>
+      <c r="B25" t="s">
+        <v>216</v>
+      </c>
+      <c r="C25" t="s">
         <v>217</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
+        <v>217</v>
+      </c>
+      <c r="E25" t="s">
+        <v>217</v>
+      </c>
+      <c r="F25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" t="s">
         <v>218</v>
       </c>
-      <c r="C25" t="s">
+      <c r="H25" t="s">
         <v>219</v>
       </c>
-      <c r="D25" t="s">
-        <v>219</v>
-      </c>
-      <c r="E25" t="s">
-        <v>219</v>
-      </c>
-      <c r="F25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="I25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" t="s">
+        <v>25</v>
+      </c>
+      <c r="K25" t="s">
         <v>220</v>
-      </c>
-      <c r="H25" t="s">
-        <v>221</v>
-      </c>
-      <c r="I25" t="s">
-        <v>25</v>
-      </c>
-      <c r="J25" t="s">
-        <v>25</v>
-      </c>
-      <c r="K25" t="s">
-        <v>222</v>
       </c>
       <c r="L25" t="s">
         <v>25</v>
@@ -2556,10 +2556,10 @@
         <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="O25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="P25" t="s">
         <v>25</v>
@@ -2568,7 +2568,7 @@
         <v>25</v>
       </c>
       <c r="R25" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
